--- a/assets/downloads/world500_retrieval_batch_02_candidate.xlsx
+++ b/assets/downloads/world500_retrieval_batch_02_candidate.xlsx
@@ -548,22 +548,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>75</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>r005_sinopecgroup</t>
+          <t>r075_shandongenergygroup</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>中国石油化工集团有限公司</t>
+          <t>山东能源集团有限公司</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>SINOPEC GROUP</t>
+          <t>SHANDONG ENERGY GROUP</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -573,7 +573,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>炼油</t>
+          <t>采矿、原油生产</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -599,7 +599,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>44</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>seed 阶段出现过候选命中：seed_review_needed，seed 候选文件为 2023-2024-EMIRATES GROUP-annual-report.pdf；当前候选池仍有 36 个近似候选项；当前 best_match_score=13</t>
+          <t>seed 阶段出现过候选命中：seed_review_needed，seed 候选文件为 2023-2024-EMIRATES GROUP-annual-report.pdf；当前候选池仍有 44 个近似候选项；当前 best_match_score=13</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>Seed stage produced a candidate hit: seed_review_needed; seed candidate file: 2023-2024-EMIRATES GROUP-annual-report.pdf; Current candidate pool still contains 36 approximate candidates; Current best_match_score=13</t>
+          <t>Seed stage produced a candidate hit: seed_review_needed; seed candidate file: 2023-2024-EMIRATES GROUP-annual-report.pdf; Current candidate pool still contains 44 approximate candidates; Current best_match_score=13</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -635,7 +635,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“中国石油化工集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“山东能源集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -652,22 +652,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>81</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>r006_chinanationalpetroleum</t>
+          <t>r081_hengligroup</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>中国石油天然气集团有限公司</t>
+          <t>恒力集团有限公司</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>CHINA NATIONAL PETROLEUM</t>
+          <t>HENGLI GROUP</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -677,7 +677,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>炼油</t>
+          <t>纺织</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -703,12 +703,12 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>41</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>13</t>
         </is>
       </c>
       <c r="O3" t="inlineStr"/>
@@ -719,12 +719,12 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>seed 阶段出现过候选命中：seed_review_needed，seed 候选文件为 2024-MONDELEZ INTERNATIONAL-Snacking-Made-Right-ESG-Report.pdf；当前候选池仍有 8 个近似候选项；当前 best_match_score=16</t>
+          <t>seed 阶段出现过候选命中：seed_review_needed，seed 候选文件为 2023-2024-EMIRATES GROUP-annual-report.pdf；当前候选池仍有 41 个近似候选项；当前 best_match_score=13</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>Seed stage produced a candidate hit: seed_review_needed; seed candidate file: 2024-MONDELEZ INTERNATIONAL-Snacking-Made-Right-ESG-Report.pdf; Current candidate pool still contains 8 approximate candidates; Current best_match_score=16</t>
+          <t>Seed stage produced a candidate hit: seed_review_needed; seed candidate file: 2023-2024-EMIRATES GROUP-annual-report.pdf; Current candidate pool still contains 41 approximate candidates; Current best_match_score=13</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“中国石油天然气集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“恒力集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -756,32 +756,32 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>83</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>r024_glencore</t>
+          <t>r083_chinapostgroup</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>嘉能可</t>
+          <t>中国邮政集团有限公司</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>GLENCORE</t>
+          <t>CHINA POST GROUP</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>瑞士</t>
+          <t>中国</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>采矿、原油生产</t>
+          <t>邮件、包裹及货物包装运输</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -799,24 +799,20 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>unmatched</t>
+          <t>seed_review_needed</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>44</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>13</t>
         </is>
       </c>
       <c r="O4" t="inlineStr"/>
@@ -827,27 +823,27 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>名单字段已标注报告下载状态：P</t>
+          <t>seed 阶段出现过候选命中：seed_review_needed，seed 候选文件为 2023-2024-EMIRATES GROUP-annual-report.pdf；当前候选池仍有 44 个近似候选项；当前 best_match_score=13</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>Registry download-status field is populated: P</t>
+          <t>Seed stage produced a candidate hit: seed_review_needed; seed candidate file: 2023-2024-EMIRATES GROUP-annual-report.pdf; Current candidate pool still contains 44 approximate candidates; Current best_match_score=13</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>优先回查原始下载台账/文件转存是否遗漏；再以母公司中英文全称、简称、official site + ESG/annual/sustainability/climate 关键词进行二次检索补库，补入后回跑 report catalog 与 diagnosis 链路。</t>
+          <t>再以母公司中英文全称、简称、official site + ESG/annual/sustainability/climate 关键词进行二次检索补库，补入后回跑 report catalog 与 diagnosis 链路。</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>First re-check the original download ledger or transfer directory for a missed file; Then run a second retrieval round with the parent-company Chinese/English name, short name, and official-site + ESG/annual/sustainability/climate keywords; rebuild the report catalog and diagnosis after backfill.</t>
+          <t>Then run a second retrieval round with the parent-company Chinese/English name, short name, and official-site + ESG/annual/sustainability/climate keywords; rebuild the report catalog and diagnosis after backfill.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“嘉能可”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“中国邮政集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -864,32 +860,32 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>138</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>r038_bankofamerica</t>
+          <t>r138_zhejiangrongshengholdinggroup</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>美国银行</t>
+          <t>浙江荣盛控股集团有限公司</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>BANK OF AMERICA</t>
+          <t>ZHEJIANG RONGSHENG HOLDING GROUP</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>美国</t>
+          <t>中国</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>银行：商业储蓄</t>
+          <t>化学品</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -915,7 +911,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>51</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -931,12 +927,12 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>seed 阶段出现过候选命中：seed_review_needed，seed 候选文件为 2023-BANK OF NEW YORK MELLON sustainability-report.pdf；当前候选池仍有 22 个近似候选项；当前 best_match_score=13</t>
+          <t>seed 阶段出现过候选命中：seed_review_needed，seed 候选文件为 2023-2024-EMIRATES GROUP-annual-report.pdf；当前候选池仍有 51 个近似候选项；当前 best_match_score=13</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>Seed stage produced a candidate hit: seed_review_needed; seed candidate file: 2023-BANK OF NEW YORK MELLON sustainability-report.pdf; Current candidate pool still contains 22 approximate candidates; Current best_match_score=13</t>
+          <t>Seed stage produced a candidate hit: seed_review_needed; seed candidate file: 2023-2024-EMIRATES GROUP-annual-report.pdf; Current candidate pool still contains 51 approximate candidates; Current best_match_score=13</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -951,7 +947,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“美国银行”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“浙江荣盛控股集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -968,32 +964,32 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>142</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>r058_fanniemae</t>
+          <t>r142_xiamenitgholdinggroup</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>房利美</t>
+          <t>厦门国贸控股集团有限公司</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>FANNIE MAE</t>
+          <t>XIAMEN ITG HOLDING GROUP</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>美国</t>
+          <t>中国</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>多元化金融</t>
+          <t>贸易</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1019,7 +1015,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>51</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1035,12 +1031,12 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>seed 阶段出现过候选命中：seed_review_needed，seed 候选文件为 Maersk Annual Report 2024.pdf；当前候选池仍有 1 个近似候选项；当前 best_match_score=13</t>
+          <t>seed 阶段出现过候选命中：seed_review_needed，seed 候选文件为 2023-2024-EMIRATES GROUP-annual-report.pdf；当前候选池仍有 51 个近似候选项；当前 best_match_score=13</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>Seed stage produced a candidate hit: seed_review_needed; seed candidate file: Maersk Annual Report 2024.pdf; Current candidate pool still contains 1 approximate candidates; Current best_match_score=13</t>
+          <t>Seed stage produced a candidate hit: seed_review_needed; seed candidate file: 2023-2024-EMIRATES GROUP-annual-report.pdf; Current candidate pool still contains 51 approximate candidates; Current best_match_score=13</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1055,7 +1051,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“房利美”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“厦门国贸控股集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1072,22 +1068,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>147</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>r059_chinalifeinsurance</t>
+          <t>r147_aviationindustrycorpofchina</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>中国人寿保险（集团）公司</t>
+          <t>中国航空工业集团有限公司</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>CHINA LIFE INSURANCE</t>
+          <t>AVIATION INDUSTRY CORP. OF CHINA</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1097,7 +1093,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>人寿与健康保险（股份）</t>
+          <t>航天与防务</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1118,12 +1114,12 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>seed_review_needed</t>
+          <t>seed_matched</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>34</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1139,12 +1135,12 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>seed 阶段出现过候选命中：seed_review_needed，seed 候选文件为 2024-MASSACHUSETTS MUTUAL LIFE INSURANCE-sustainabilityreport.pdf；当前候选池仍有 8 个近似候选项；当前 best_match_score=16</t>
+          <t>seed 阶段出现过候选命中：seed_matched，seed 候选文件为 2025 DAIWA HOUSE INDUSTRY_Sustainability_All.pdf；当前候选池仍有 34 个近似候选项；当前 best_match_score=16</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>Seed stage produced a candidate hit: seed_review_needed; seed candidate file: 2024-MASSACHUSETTS MUTUAL LIFE INSURANCE-sustainabilityreport.pdf; Current candidate pool still contains 8 approximate candidates; Current best_match_score=16</t>
+          <t>Seed stage produced a candidate hit: seed_matched; seed candidate file: 2025 DAIWA HOUSE INDUSTRY_Sustainability_All.pdf; Current candidate pool still contains 34 approximate candidates; Current best_match_score=16</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1159,7 +1155,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“中国人寿保险（集团）公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“中国航空工业集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1176,32 +1172,32 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>155</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>r075_shandongenergygroup</t>
+          <t>r155_energytransfer公司</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>山东能源集团有限公司</t>
+          <t>Energy Transfer公司</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>SHANDONG ENERGY GROUP</t>
+          <t>Energy Transfer公司</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>中国</t>
+          <t>美国</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>采矿、原油生产</t>
+          <t>管道运输</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1227,7 +1223,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1243,12 +1239,12 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>seed 阶段出现过候选命中：seed_review_needed，seed 候选文件为 2023-2024-EMIRATES GROUP-annual-report.pdf；当前候选池仍有 39 个近似候选项；当前 best_match_score=13</t>
+          <t>seed 阶段出现过候选命中：seed_review_needed，seed 候选文件为 2023_SUNCOR ENERGY_sustainability_report.pdf；当前候选池仍有 3 个近似候选项；当前 best_match_score=13</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>Seed stage produced a candidate hit: seed_review_needed; seed candidate file: 2023-2024-EMIRATES GROUP-annual-report.pdf; Current candidate pool still contains 39 approximate candidates; Current best_match_score=13</t>
+          <t>Seed stage produced a candidate hit: seed_review_needed; seed candidate file: 2023_SUNCOR ENERGY_sustainability_report.pdf; Current candidate pool still contains 3 approximate candidates; Current best_match_score=13</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1263,7 +1259,7 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“山东能源集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“Energy Transfer公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1280,22 +1276,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>160</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>r081_hengligroup</t>
+          <t>r160_chinanorthindustriesgroup</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>恒力集团有限公司</t>
+          <t>中国兵器工业集团有限公司</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>HENGLI GROUP</t>
+          <t>CHINA NORTH INDUSTRIES GROUP</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1305,7 +1301,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>纺织</t>
+          <t>航天与防务</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1326,17 +1322,17 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>seed_review_needed</t>
+          <t>seed_matched</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>46</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>16</t>
         </is>
       </c>
       <c r="O9" t="inlineStr"/>
@@ -1347,12 +1343,12 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>seed 阶段出现过候选命中：seed_review_needed，seed 候选文件为 2023-2024-EMIRATES GROUP-annual-report.pdf；当前候选池仍有 36 个近似候选项；当前 best_match_score=13</t>
+          <t>seed 阶段出现过候选命中：seed_matched，seed 候选文件为 2024-LYONDELLBASELL INDUSTRIES-sustainability-report.pdf；当前候选池仍有 46 个近似候选项；当前 best_match_score=16</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>Seed stage produced a candidate hit: seed_review_needed; seed candidate file: 2023-2024-EMIRATES GROUP-annual-report.pdf; Current candidate pool still contains 36 approximate candidates; Current best_match_score=13</t>
+          <t>Seed stage produced a candidate hit: seed_matched; seed candidate file: 2024-LYONDELLBASELL INDUSTRIES-sustainability-report.pdf; Current candidate pool still contains 46 approximate candidates; Current best_match_score=16</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1367,7 +1363,7 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“恒力集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“中国兵器工业集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1384,22 +1380,22 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>161</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>r083_chinapostgroup</t>
+          <t>r161_pacificconstructiongroup</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>中国邮政集团有限公司</t>
+          <t>太平洋建设集团有限公司</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>CHINA POST GROUP</t>
+          <t>PACIFIC CONSTRUCTION GROUP</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1409,7 +1405,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>邮件、包裹及货物包装运输</t>
+          <t>工程与建筑</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1435,7 +1431,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>41</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1451,12 +1447,12 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>seed 阶段出现过候选命中：seed_review_needed，seed 候选文件为 2023-2024-EMIRATES GROUP-annual-report.pdf；当前候选池仍有 38 个近似候选项；当前 best_match_score=13</t>
+          <t>seed 阶段出现过候选命中：seed_review_needed，seed 候选文件为 2023-2024-EMIRATES GROUP-annual-report.pdf；当前候选池仍有 41 个近似候选项；当前 best_match_score=13</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>Seed stage produced a candidate hit: seed_review_needed; seed candidate file: 2023-2024-EMIRATES GROUP-annual-report.pdf; Current candidate pool still contains 38 approximate candidates; Current best_match_score=13</t>
+          <t>Seed stage produced a candidate hit: seed_review_needed; seed candidate file: 2023-2024-EMIRATES GROUP-annual-report.pdf; Current candidate pool still contains 41 approximate candidates; Current best_match_score=13</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1471,7 +1467,7 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“中国邮政集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“太平洋建设集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1488,32 +1484,32 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>175</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>r087_goldmansachsgroup</t>
+          <t>r175_shandongweiqiaopioneeringgroup</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>高盛集团</t>
+          <t>山东魏桥创业集团有限公司</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>GOLDMAN SACHS GROUP</t>
+          <t>SHANDONG WEIQIAO PIONEERING GROUP</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>美国</t>
+          <t>中国</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>银行：商业储蓄</t>
+          <t>纺织</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1539,7 +1535,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>41</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1555,12 +1551,12 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>seed 阶段出现过候选命中：seed_review_needed，seed 候选文件为 2023-2024-EMIRATES GROUP-annual-report.pdf；当前候选池仍有 36 个近似候选项；当前 best_match_score=13</t>
+          <t>seed 阶段出现过候选命中：seed_review_needed，seed 候选文件为 2023-2024-EMIRATES GROUP-annual-report.pdf；当前候选池仍有 41 个近似候选项；当前 best_match_score=13</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>Seed stage produced a candidate hit: seed_review_needed; seed candidate file: 2023-2024-EMIRATES GROUP-annual-report.pdf; Current candidate pool still contains 36 approximate candidates; Current best_match_score=13</t>
+          <t>Seed stage produced a candidate hit: seed_review_needed; seed candidate file: 2023-2024-EMIRATES GROUP-annual-report.pdf; Current candidate pool still contains 41 approximate candidates; Current best_match_score=13</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1575,7 +1571,7 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“高盛集团”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“山东魏桥创业集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1592,32 +1588,32 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>180</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>r094_statefarminsurance</t>
+          <t>r180_oilandnaturalgas</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>州立农业保险公司</t>
+          <t>印度石油天然气公司</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>STATE FARM INSURANCE</t>
+          <t>OIL &amp; NATURAL GAS</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>美国</t>
+          <t>印度</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>财产与意外保险（互助）</t>
+          <t>采矿、原油生产</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1643,12 +1639,12 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>26</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>13</t>
         </is>
       </c>
       <c r="O12" t="inlineStr"/>
@@ -1659,12 +1655,12 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>seed 阶段出现过候选命中：seed_review_needed，seed 候选文件为 2024-MASSACHUSETTS MUTUAL LIFE INSURANCE-sustainabilityreport.pdf；当前候选池仍有 12 个近似候选项；当前 best_match_score=16</t>
+          <t>seed 阶段出现过候选命中：seed_review_needed，seed 候选文件为 2024 STANDARD CHARTERED sustainable-finance-impact-report.pdf；当前候选池仍有 26 个近似候选项；当前 best_match_score=13</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>Seed stage produced a candidate hit: seed_review_needed; seed candidate file: 2024-MASSACHUSETTS MUTUAL LIFE INSURANCE-sustainabilityreport.pdf; Current candidate pool still contains 12 approximate candidates; Current best_match_score=16</t>
+          <t>Seed stage produced a candidate hit: seed_review_needed; seed candidate file: 2024 STANDARD CHARTERED sustainable-finance-impact-report.pdf; Current candidate pool still contains 26 approximate candidates; Current best_match_score=13</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1679,7 +1675,7 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“州立农业保险公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“印度石油天然气公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -1696,32 +1692,32 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>213</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>r095_lifeinsurancecorpofindia</t>
+          <t>r213_jinnengholdinggroup</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>印度人寿保险公司</t>
+          <t>晋能控股集团有限公司</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>LIFE INSURANCE CORP. OF INDIA</t>
+          <t>JINNENG HOLDING GROUP</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>印度</t>
+          <t>中国</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>人寿与健康保险（股份）</t>
+          <t>采矿、原油生产</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1747,12 +1743,12 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>51</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>13</t>
         </is>
       </c>
       <c r="O13" t="inlineStr"/>
@@ -1763,12 +1759,12 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>seed 阶段出现过候选命中：seed_review_needed，seed 候选文件为 2024-MASSACHUSETTS MUTUAL LIFE INSURANCE-sustainabilityreport.pdf；当前候选池仍有 34 个近似候选项；当前 best_match_score=16</t>
+          <t>seed 阶段出现过候选命中：seed_review_needed，seed 候选文件为 2023-2024-EMIRATES GROUP-annual-report.pdf；当前候选池仍有 51 个近似候选项；当前 best_match_score=13</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>Seed stage produced a candidate hit: seed_review_needed; seed candidate file: 2024-MASSACHUSETTS MUTUAL LIFE INSURANCE-sustainabilityreport.pdf; Current candidate pool still contains 34 approximate candidates; Current best_match_score=16</t>
+          <t>Seed stage produced a candidate hit: seed_review_needed; seed candidate file: 2023-2024-EMIRATES GROUP-annual-report.pdf; Current candidate pool still contains 51 approximate candidates; Current best_match_score=13</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1783,7 +1779,7 @@
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“印度人寿保险公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“晋能控股集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -1800,32 +1796,32 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>219</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>r100_sk集团</t>
+          <t>r219_internationalbusinessmachines</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>SK集团</t>
+          <t>国际商业机器公司</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>SK集团</t>
+          <t>INTERNATIONAL BUSINESS MACHINES</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>韩国</t>
+          <t>美国</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>炼油</t>
+          <t>信息技术服务</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1843,24 +1839,20 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
+      <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>unmatched</t>
+          <t>seed_review_needed</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>16</t>
         </is>
       </c>
       <c r="O14" t="inlineStr"/>
@@ -1871,27 +1863,27 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>名单字段已标注报告下载状态：P</t>
+          <t>seed 阶段出现过候选命中：seed_review_needed，seed 候选文件为 2024-MONDELEZ INTERNATIONAL-Snacking-Made-Right-ESG-Report.pdf；当前候选池仍有 6 个近似候选项；当前 best_match_score=16</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>Registry download-status field is populated: P</t>
+          <t>Seed stage produced a candidate hit: seed_review_needed; seed candidate file: 2024-MONDELEZ INTERNATIONAL-Snacking-Made-Right-ESG-Report.pdf; Current candidate pool still contains 6 approximate candidates; Current best_match_score=16</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>优先回查原始下载台账/文件转存是否遗漏；再以母公司中英文全称、简称、official site + ESG/annual/sustainability/climate 关键词进行二次检索补库，补入后回跑 report catalog 与 diagnosis 链路。</t>
+          <t>再以母公司中英文全称、简称、official site + ESG/annual/sustainability/climate 关键词进行二次检索补库，补入后回跑 report catalog 与 diagnosis 链路。</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>First re-check the original download ledger or transfer directory for a missed file; Then run a second retrieval round with the parent-company Chinese/English name, short name, and official-site + ESG/annual/sustainability/climate keywords; rebuild the report catalog and diagnosis after backfill.</t>
+          <t>Then run a second retrieval round with the parent-company Chinese/English name, short name, and official-site + ESG/annual/sustainability/climate keywords; rebuild the report catalog and diagnosis after backfill.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“SK集团”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“国际商业机器公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
@@ -1908,22 +1900,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>238</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>r103_huaweiinvestmentandholding</t>
+          <t>r238_chinahuanenggroup</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>华为投资控股有限公司</t>
+          <t>中国华能集团有限公司</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>HUAWEI INVESTMENT &amp; HOLDING</t>
+          <t>CHINA HUANENG GROUP</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1933,7 +1925,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>网络、通讯设备</t>
+          <t>能源</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1959,7 +1951,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>43</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1967,20 +1959,24 @@
           <t>13</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr"/>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>AIA GROUP-Main-ESG-Report_CH.pdf</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>29</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>seed 阶段出现过候选命中：seed_review_needed，seed 候选文件为 2024 STANDARD CHARTERED sustainable-finance-impact-report.pdf；当前候选池仍有 31 个近似候选项；当前 best_match_score=13</t>
+          <t>seed 阶段出现过候选命中：seed_review_needed，seed 候选文件为 2023-2024-EMIRATES GROUP-annual-report.pdf；当前候选池仍有 43 个近似候选项；当前 best_match_score=13；review 队列里出现过近似推荐文件：AIA GROUP-Main-ESG-Report_CH.pdf</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>Seed stage produced a candidate hit: seed_review_needed; seed candidate file: 2024 STANDARD CHARTERED sustainable-finance-impact-report.pdf; Current candidate pool still contains 31 approximate candidates; Current best_match_score=13</t>
+          <t>Seed stage produced a candidate hit: seed_review_needed; seed candidate file: 2023-2024-EMIRATES GROUP-annual-report.pdf; Current candidate pool still contains 43 approximate candidates; Current best_match_score=13; Review queue contains a higher-scored approximate recommendation: AIA GROUP-Main-ESG-Report_CH.pdf</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -1995,7 +1991,7 @@
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“华为投资控股有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“中国华能集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
@@ -2012,32 +2008,32 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>239</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>r119_christiandior</t>
+          <t>r239_chinaenergyengineeringgroup</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>迪奥公司</t>
+          <t>中国能源建设集团有限公司</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>CHRISTIAN DIOR</t>
+          <t>CHINA ENERGY ENGINEERING GROUP</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>法国</t>
+          <t>中国</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>服装</t>
+          <t>工程与建筑</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2055,24 +2051,20 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
+      <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>unmatched</t>
+          <t>seed_review_needed</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>46</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>13</t>
         </is>
       </c>
       <c r="O16" t="inlineStr"/>
@@ -2083,27 +2075,27 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>名单字段已标注报告下载状态：P</t>
+          <t>seed 阶段出现过候选命中：seed_review_needed，seed 候选文件为 2023-2024-EMIRATES GROUP-annual-report.pdf；当前候选池仍有 46 个近似候选项；当前 best_match_score=13</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>Registry download-status field is populated: P</t>
+          <t>Seed stage produced a candidate hit: seed_review_needed; seed candidate file: 2023-2024-EMIRATES GROUP-annual-report.pdf; Current candidate pool still contains 46 approximate candidates; Current best_match_score=13</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>优先回查原始下载台账/文件转存是否遗漏；再以母公司中英文全称、简称、official site + ESG/annual/sustainability/climate 关键词进行二次检索补库，补入后回跑 report catalog 与 diagnosis 链路。</t>
+          <t>再以母公司中英文全称、简称、official site + ESG/annual/sustainability/climate 关键词进行二次检索补库，补入后回跑 report catalog 与 diagnosis 链路。</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>First re-check the original download ledger or transfer directory for a missed file; Then run a second retrieval round with the parent-company Chinese/English name, short name, and official-site + ESG/annual/sustainability/climate keywords; rebuild the report catalog and diagnosis after backfill.</t>
+          <t>Then run a second retrieval round with the parent-company Chinese/English name, short name, and official-site + ESG/annual/sustainability/climate keywords; rebuild the report catalog and diagnosis after backfill.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“迪奥公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“中国能源建设集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
@@ -2120,32 +2112,32 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>240</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>r122_carrefour</t>
+          <t>r240_dongfengmotor</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>家乐福</t>
+          <t>东风汽车集团有限公司</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>CARREFOUR</t>
+          <t>DONGFENG MOTOR</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>法国</t>
+          <t>中国</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>食品店和杂货店</t>
+          <t>车辆与零部件</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2163,24 +2155,20 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
+      <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>unmatched</t>
+          <t>seed_review_needed</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>13</t>
         </is>
       </c>
       <c r="O17" t="inlineStr"/>
@@ -2191,27 +2179,27 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>名单字段已标注报告下载状态：P</t>
+          <t>seed 阶段出现过候选命中：seed_review_needed，seed 候选文件为 2024_MAZDA MOTOR_Sustainability_Report.pdf；当前候选池仍有 7 个近似候选项；当前 best_match_score=13</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>Registry download-status field is populated: P</t>
+          <t>Seed stage produced a candidate hit: seed_review_needed; seed candidate file: 2024_MAZDA MOTOR_Sustainability_Report.pdf; Current candidate pool still contains 7 approximate candidates; Current best_match_score=13</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>优先回查原始下载台账/文件转存是否遗漏；再以母公司中英文全称、简称、official site + ESG/annual/sustainability/climate 关键词进行二次检索补库，补入后回跑 report catalog 与 diagnosis 链路。</t>
+          <t>再以母公司中英文全称、简称、official site + ESG/annual/sustainability/climate 关键词进行二次检索补库，补入后回跑 report catalog 与 diagnosis 链路。</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>First re-check the original download ledger or transfer directory for a missed file; Then run a second retrieval round with the parent-company Chinese/English name, short name, and official-site + ESG/annual/sustainability/climate keywords; rebuild the report catalog and diagnosis after backfill.</t>
+          <t>Then run a second retrieval round with the parent-company Chinese/English name, short name, and official-site + ESG/annual/sustainability/climate keywords; rebuild the report catalog and diagnosis after backfill.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“家乐福”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“东风汽车集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
@@ -2228,22 +2216,22 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>243</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>r129_chinafawgroup</t>
+          <t>r243_zhejianghengyigroup</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>中国第一汽车集团有限公司</t>
+          <t>浙江恒逸集团有限公司</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>CHINA FAW GROUP</t>
+          <t>ZHEJIANG HENGYI GROUP</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -2253,7 +2241,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>车辆与零部件</t>
+          <t>化学品</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2279,7 +2267,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>41</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2287,20 +2275,24 @@
           <t>13</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr"/>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>Geely-Holding-Group-Sustainability-Report-2024-ZH.pdf</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>31</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>seed 阶段出现过候选命中：seed_review_needed，seed 候选文件为 2023-2024-EMIRATES GROUP-annual-report.pdf；当前候选池仍有 37 个近似候选项；当前 best_match_score=13</t>
+          <t>seed 阶段出现过候选命中：seed_review_needed，seed 候选文件为 2023-2024-EMIRATES GROUP-annual-report.pdf；当前候选池仍有 41 个近似候选项；当前 best_match_score=13；review 队列里出现过近似推荐文件：Geely-Holding-Group-Sustainability-Report-2024-ZH.pdf</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>Seed stage produced a candidate hit: seed_review_needed; seed candidate file: 2023-2024-EMIRATES GROUP-annual-report.pdf; Current candidate pool still contains 37 approximate candidates; Current best_match_score=13</t>
+          <t>Seed stage produced a candidate hit: seed_review_needed; seed candidate file: 2023-2024-EMIRATES GROUP-annual-report.pdf; Current candidate pool still contains 41 approximate candidates; Current best_match_score=13; Review queue contains a higher-scored approximate recommendation: Geely-Holding-Group-Sustainability-Report-2024-ZH.pdf</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2315,7 +2307,7 @@
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“中国第一汽车集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“浙江恒逸集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
@@ -2332,22 +2324,22 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>249</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>r138_zhejiangrongshengholdinggroup</t>
+          <t>r249_hbisgroup</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>浙江荣盛控股集团有限公司</t>
+          <t>河钢集团有限公司</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>ZHEJIANG RONGSHENG HOLDING GROUP</t>
+          <t>HBIS GROUP</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -2357,7 +2349,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>化学品</t>
+          <t>金属产品</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2383,7 +2375,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>41</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -2399,12 +2391,12 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>seed 阶段出现过候选命中：seed_review_needed，seed 候选文件为 2023-2024-EMIRATES GROUP-annual-report.pdf；当前候选池仍有 46 个近似候选项；当前 best_match_score=13</t>
+          <t>seed 阶段出现过候选命中：seed_review_needed，seed 候选文件为 2023-2024-EMIRATES GROUP-annual-report.pdf；当前候选池仍有 41 个近似候选项；当前 best_match_score=13</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>Seed stage produced a candidate hit: seed_review_needed; seed candidate file: 2023-2024-EMIRATES GROUP-annual-report.pdf; Current candidate pool still contains 46 approximate candidates; Current best_match_score=13</t>
+          <t>Seed stage produced a candidate hit: seed_review_needed; seed candidate file: 2023-2024-EMIRATES GROUP-annual-report.pdf; Current candidate pool still contains 41 approximate candidates; Current best_match_score=13</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2419,7 +2411,7 @@
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“浙江荣盛控股集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“河钢集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
@@ -2436,22 +2428,22 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>142</t>
+          <t>253</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>r142_xiamenitgholdinggroup</t>
+          <t>r253_chinaelectronicstechnologygroup</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>厦门国贸控股集团有限公司</t>
+          <t>中国电子科技集团有限公司</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>XIAMEN ITG HOLDING GROUP</t>
+          <t>CHINA ELECTRONICS TECHNOLOGY GROUP</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -2461,7 +2453,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>贸易</t>
+          <t>航天与防务</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2487,12 +2479,12 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>45</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>16</t>
         </is>
       </c>
       <c r="O20" t="inlineStr"/>
@@ -2503,12 +2495,12 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>seed 阶段出现过候选命中：seed_review_needed，seed 候选文件为 2023-2024-EMIRATES GROUP-annual-report.pdf；当前候选池仍有 46 个近似候选项；当前 best_match_score=13</t>
+          <t>seed 阶段出现过候选命中：seed_review_needed，seed 候选文件为 2024-ARROW ELECTRONICS-Corporate-Stewardship-and-Impact-Report-1.pdf；当前候选池仍有 45 个近似候选项；当前 best_match_score=16</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>Seed stage produced a candidate hit: seed_review_needed; seed candidate file: 2023-2024-EMIRATES GROUP-annual-report.pdf; Current candidate pool still contains 46 approximate candidates; Current best_match_score=13</t>
+          <t>Seed stage produced a candidate hit: seed_review_needed; seed candidate file: 2024-ARROW ELECTRONICS-Corporate-Stewardship-and-Impact-Report-1.pdf; Current candidate pool still contains 45 approximate candidates; Current best_match_score=16</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2523,7 +2515,7 @@
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“厦门国贸控股集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“中国电子科技集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
@@ -2540,22 +2532,22 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>147</t>
+          <t>265</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>r147_aviationindustrycorpofchina</t>
+          <t>r265_tsingshanholdinggroup</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>中国航空工业集团有限公司</t>
+          <t>青山控股集团有限公司</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AVIATION INDUSTRY CORP. OF CHINA</t>
+          <t>TSINGSHAN HOLDING GROUP</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -2565,7 +2557,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>航天与防务</t>
+          <t>金属产品</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2586,17 +2578,17 @@
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr">
         <is>
-          <t>seed_matched</t>
+          <t>seed_review_needed</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>51</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>13</t>
         </is>
       </c>
       <c r="O21" t="inlineStr"/>
@@ -2607,12 +2599,12 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>seed 阶段出现过候选命中：seed_matched，seed 候选文件为 2025 DAIWA HOUSE INDUSTRY_Sustainability_All.pdf；当前候选池仍有 29 个近似候选项；当前 best_match_score=16</t>
+          <t>seed 阶段出现过候选命中：seed_review_needed，seed 候选文件为 2023-2024-EMIRATES GROUP-annual-report.pdf；当前候选池仍有 51 个近似候选项；当前 best_match_score=13</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>Seed stage produced a candidate hit: seed_matched; seed candidate file: 2025 DAIWA HOUSE INDUSTRY_Sustainability_All.pdf; Current candidate pool still contains 29 approximate candidates; Current best_match_score=16</t>
+          <t>Seed stage produced a candidate hit: seed_review_needed; seed candidate file: 2023-2024-EMIRATES GROUP-annual-report.pdf; Current candidate pool still contains 51 approximate candidates; Current best_match_score=13</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2627,7 +2619,7 @@
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“中国航空工业集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“青山控股集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
@@ -2644,32 +2636,32 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>267</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>r155_energytransfer公司</t>
+          <t>r267_coscoshipping</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Energy Transfer公司</t>
+          <t>中国远洋海运集团有限公司</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Energy Transfer公司</t>
+          <t>COSCO SHIPPING</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>美国</t>
+          <t>中国</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>管道运输</t>
+          <t>船务</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2687,20 +2679,24 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>seed_review_needed</t>
+          <t>unmatched</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>4</t>
         </is>
       </c>
       <c r="O22" t="inlineStr"/>
@@ -2711,27 +2707,27 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>seed 阶段出现过候选命中：seed_review_needed，seed 候选文件为 2023_SUNCOR ENERGY_sustainability_report.pdf；当前候选池仍有 3 个近似候选项；当前 best_match_score=13</t>
+          <t>名单字段已标注报告下载状态：P</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>Seed stage produced a candidate hit: seed_review_needed; seed candidate file: 2023_SUNCOR ENERGY_sustainability_report.pdf; Current candidate pool still contains 3 approximate candidates; Current best_match_score=13</t>
+          <t>Registry download-status field is populated: P</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>再以母公司中英文全称、简称、official site + ESG/annual/sustainability/climate 关键词进行二次检索补库，补入后回跑 report catalog 与 diagnosis 链路。</t>
+          <t>优先回查原始下载台账/文件转存是否遗漏；再以母公司中英文全称、简称、official site + ESG/annual/sustainability/climate 关键词进行二次检索补库，补入后回跑 report catalog 与 diagnosis 链路。</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>Then run a second retrieval round with the parent-company Chinese/English name, short name, and official-site + ESG/annual/sustainability/climate keywords; rebuild the report catalog and diagnosis after backfill.</t>
+          <t>First re-check the original download ledger or transfer directory for a missed file; Then run a second retrieval round with the parent-company Chinese/English name, short name, and official-site + ESG/annual/sustainability/climate keywords; rebuild the report catalog and diagnosis after backfill.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“Energy Transfer公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“中国远洋海运集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
@@ -2748,22 +2744,22 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>277</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>r160_chinanorthindustriesgroup</t>
+          <t>r277_mideagroup</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>中国兵器工业集团有限公司</t>
+          <t>美的集团股份有限公司</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>CHINA NORTH INDUSTRIES GROUP</t>
+          <t>MIDEA GROUP</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2773,7 +2769,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>航天与防务</t>
+          <t>电子、电气设备</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2794,17 +2790,17 @@
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr">
         <is>
-          <t>seed_matched</t>
+          <t>seed_review_needed</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>41</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>13</t>
         </is>
       </c>
       <c r="O23" t="inlineStr"/>
@@ -2815,12 +2811,12 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>seed 阶段出现过候选命中：seed_matched，seed 候选文件为 2024-LYONDELLBASELL INDUSTRIES-sustainability-report.pdf；当前候选池仍有 40 个近似候选项；当前 best_match_score=16</t>
+          <t>seed 阶段出现过候选命中：seed_review_needed，seed 候选文件为 2023-2024-EMIRATES GROUP-annual-report.pdf；当前候选池仍有 41 个近似候选项；当前 best_match_score=13</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>Seed stage produced a candidate hit: seed_matched; seed candidate file: 2024-LYONDELLBASELL INDUSTRIES-sustainability-report.pdf; Current candidate pool still contains 40 approximate candidates; Current best_match_score=16</t>
+          <t>Seed stage produced a candidate hit: seed_review_needed; seed candidate file: 2023-2024-EMIRATES GROUP-annual-report.pdf; Current candidate pool still contains 41 approximate candidates; Current best_match_score=13</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -2835,7 +2831,7 @@
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“中国兵器工业集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“美的集团股份有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
@@ -2852,22 +2848,22 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>279</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>r161_pacificconstructiongroup</t>
+          <t>r279_chinaunitednetworkcommunications</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>太平洋建设集团有限公司</t>
+          <t>中国联合网络通信股份有限公司</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>PACIFIC CONSTRUCTION GROUP</t>
+          <t>CHINA UNITED NETWORK COMMUNICATIONS</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2877,7 +2873,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>工程与建筑</t>
+          <t>电信</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2898,17 +2894,17 @@
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr">
         <is>
-          <t>seed_review_needed</t>
+          <t>seed_matched</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>7</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>16</t>
         </is>
       </c>
       <c r="O24" t="inlineStr"/>
@@ -2919,12 +2915,12 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>seed 阶段出现过候选命中：seed_review_needed，seed 候选文件为 2023-2024-EMIRATES GROUP-annual-report.pdf；当前候选池仍有 36 个近似候选项；当前 best_match_score=13</t>
+          <t>seed 阶段出现过候选命中：seed_matched，seed 候选文件为 2023 CHARTER COMMUNICATIONS esg-report.pdf；当前候选池仍有 7 个近似候选项；当前 best_match_score=16</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>Seed stage produced a candidate hit: seed_review_needed; seed candidate file: 2023-2024-EMIRATES GROUP-annual-report.pdf; Current candidate pool still contains 36 approximate candidates; Current best_match_score=13</t>
+          <t>Seed stage produced a candidate hit: seed_matched; seed candidate file: 2023 CHARTER COMMUNICATIONS esg-report.pdf; Current candidate pool still contains 7 approximate candidates; Current best_match_score=16</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -2939,7 +2935,7 @@
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“太平洋建设集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“中国联合网络通信股份有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
@@ -2956,32 +2952,32 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>175</t>
+          <t>280</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>r175_shandongweiqiaopioneeringgroup</t>
+          <t>r280_libertymutualinsurancegroup</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>山东魏桥创业集团有限公司</t>
+          <t>美国利宝互助保险集团</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>SHANDONG WEIQIAO PIONEERING GROUP</t>
+          <t>LIBERTY MUTUAL INSURANCE GROUP</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>中国</t>
+          <t>美国</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>纺织</t>
+          <t>财产与意外保险（股份）</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3007,12 +3003,12 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>46</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>16</t>
         </is>
       </c>
       <c r="O25" t="inlineStr"/>
@@ -3023,12 +3019,12 @@
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>seed 阶段出现过候选命中：seed_review_needed，seed 候选文件为 2023-2024-EMIRATES GROUP-annual-report.pdf；当前候选池仍有 36 个近似候选项；当前 best_match_score=13</t>
+          <t>seed 阶段出现过候选命中：seed_review_needed，seed 候选文件为 2024-MASSACHUSETTS MUTUAL LIFE INSURANCE-sustainabilityreport.pdf；当前候选池仍有 46 个近似候选项；当前 best_match_score=16</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>Seed stage produced a candidate hit: seed_review_needed; seed candidate file: 2023-2024-EMIRATES GROUP-annual-report.pdf; Current candidate pool still contains 36 approximate candidates; Current best_match_score=13</t>
+          <t>Seed stage produced a candidate hit: seed_review_needed; seed candidate file: 2024-MASSACHUSETTS MUTUAL LIFE INSURANCE-sustainabilityreport.pdf; Current candidate pool still contains 46 approximate candidates; Current best_match_score=16</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -3043,7 +3039,7 @@
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“山东魏桥创业集团有限公司”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“美国利宝互助保险集团”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
@@ -3060,27 +3056,27 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>178</t>
+          <t>281</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>r178_statebankofindia</t>
+          <t>r281_bankofnovascotia</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>印度国家银行</t>
+          <t>加拿大丰业银行</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>STATE BANK OF INDIA</t>
+          <t>BANK OF NOVA SCOTIA</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>印度</t>
+          <t>加拿大</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -3111,7 +3107,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -3127,12 +3123,12 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>seed 阶段出现过候选命中：seed_review_needed，seed 候选文件为 2023-BANK OF NEW YORK MELLON sustainability-report.pdf；当前候选池仍有 25 个近似候选项；当前 best_match_score=13</t>
+          <t>seed 阶段出现过候选命中：seed_review_needed，seed 候选文件为 2023-BANK OF NEW YORK MELLON sustainability-report.pdf；当前候选池仍有 24 个近似候选项；当前 best_match_score=13</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>Seed stage produced a candidate hit: seed_review_needed; seed candidate file: 2023-BANK OF NEW YORK MELLON sustainability-report.pdf; Current candidate pool still contains 25 approximate candidates; Current best_match_score=13</t>
+          <t>Seed stage produced a candidate hit: seed_review_needed; seed candidate file: 2023-BANK OF NEW YORK MELLON sustainability-report.pdf; Current candidate pool still contains 24 approximate candidates; Current best_match_score=13</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3147,7 +3143,7 @@
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>在当前库存文件中，未检出能够安全归属于“印度国家银行”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
+          <t>在当前库存文件中，未检出能够安全归属于“加拿大丰业银行”母公司的主报告文件；现有文件名检索结果不足以支持人工硬配。</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
